--- a/output/StructureDefinition-pdex-provider-group.xlsx
+++ b/output/StructureDefinition-pdex-provider-group.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AL$71</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AL$68</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2470" uniqueCount="449">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2365" uniqueCount="431">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.1.1</t>
+    <t>2.2.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-17T14:48:28-05:00</t>
+    <t>2026-03-17T22:49:33-04:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -93,7 +93,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>The Provider Attribution Group List. Based on the Da Vinci Attribution Group (ATRGroup) Profile with the addition of extensions to track latest download for a member. Each member element in the Group record, that is processed by the export operation, should be updated with the execution date/time in lastTransmitted, list of resources (resourceTypes) in lastResources and query filters (filterQueries) in lastFilters.</t>
+    <t>The Provider Attribution Group List. Based on the Da Vinci Attribution Group (ATRGroup) Profile. The member element represents the patients attributed to the provider for data access purposes.</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -1315,63 +1315,6 @@
   </si>
   <si>
     <t>Indicates the attributed provider.</t>
-  </si>
-  <si>
-    <t>Group.member.extension:lastTransmitted</t>
-  </si>
-  <si>
-    <t>lastTransmitted</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {http://hl7.org/fhir/us/davinci-pdex/StructureDefinition/base-ext-last-transmission}
-</t>
-  </si>
-  <si>
-    <t>Member Last Transmission</t>
-  </si>
-  <si>
-    <t>Indicates the last date/time that data ware requested and transmitted for a member as part of a data delta access request.</t>
-  </si>
-  <si>
-    <t>Use the data/time of execution of the #DavinciDataexport operation</t>
-  </si>
-  <si>
-    <t>Group.member.extension:lastResources</t>
-  </si>
-  <si>
-    <t>lastResources</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {http://hl7.org/fhir/us/davinci-pdex/StructureDefinition/base-ext-last-types}
-</t>
-  </si>
-  <si>
-    <t>Member Last Resource Types</t>
-  </si>
-  <si>
-    <t>Indicates the resources exported in the last export operation. This string can be taken from the DaVinci Data Export Request _type Parameter.</t>
-  </si>
-  <si>
-    <t>Take the comma-delimited string value from the $DaVinci-data-export.resourceTypes parameter in the operation request.</t>
-  </si>
-  <si>
-    <t>Group.member.extension:lastFilters</t>
-  </si>
-  <si>
-    <t>lastFilters</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {http://hl7.org/fhir/us/davinci-pdex/StructureDefinition/base-ext-last-typefilter}
-</t>
-  </si>
-  <si>
-    <t>Member Last Resource Filters</t>
-  </si>
-  <si>
-    <t>Indicates the filters applied to the resources exported in the last export operation. This string can be taken from the DaVinci Data Export Request _typeFilter Parameter.</t>
-  </si>
-  <si>
-    <t>Take the comma-delimited string value from the $DaVinci-data-export.filterQueries parameter in the operation request.</t>
   </si>
   <si>
     <t>Group.member.modifierExtension</t>
@@ -1754,7 +1697,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AL71"/>
+  <dimension ref="A1:AL68"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="35.43359375" customWidth="true" bestFit="true"/>
@@ -8724,48 +8667,48 @@
         <v>79</v>
       </c>
     </row>
-    <row r="65">
+    <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
         <v>416</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>396</v>
-      </c>
-      <c r="C65" t="s" s="2">
-        <v>417</v>
-      </c>
+        <v>416</v>
+      </c>
+      <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
-        <v>79</v>
+        <v>356</v>
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G65" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="H65" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I65" t="s" s="2">
         <v>90</v>
       </c>
-      <c r="I65" t="s" s="2">
-        <v>79</v>
-      </c>
       <c r="J65" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>418</v>
+        <v>110</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>419</v>
+        <v>357</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>420</v>
+        <v>358</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>421</v>
-      </c>
-      <c r="O65" s="2"/>
+        <v>113</v>
+      </c>
+      <c r="O65" t="s" s="2">
+        <v>217</v>
+      </c>
       <c r="P65" t="s" s="2">
         <v>79</v>
       </c>
@@ -8813,7 +8756,7 @@
         <v>79</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>117</v>
+        <v>359</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>80</v>
@@ -8828,7 +8771,7 @@
         <v>118</v>
       </c>
       <c r="AK65" t="s" s="2">
-        <v>79</v>
+        <v>188</v>
       </c>
       <c r="AL65" t="s" s="2">
         <v>79</v>
@@ -8836,20 +8779,18 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>422</v>
+        <v>417</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>396</v>
-      </c>
-      <c r="C66" t="s" s="2">
-        <v>423</v>
-      </c>
+        <v>417</v>
+      </c>
+      <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
         <v>79</v>
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="G66" t="s" s="2">
         <v>89</v>
@@ -8864,17 +8805,15 @@
         <v>79</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>424</v>
+        <v>418</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>425</v>
+        <v>419</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>426</v>
-      </c>
-      <c r="N66" t="s" s="2">
-        <v>427</v>
-      </c>
+        <v>420</v>
+      </c>
+      <c r="N66" s="2"/>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
         <v>79</v>
@@ -8923,19 +8862,19 @@
         <v>79</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>117</v>
+        <v>417</v>
       </c>
       <c r="AG66" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AH66" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="AI66" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>118</v>
+        <v>101</v>
       </c>
       <c r="AK66" t="s" s="2">
         <v>79</v>
@@ -8946,14 +8885,12 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>428</v>
+        <v>421</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>396</v>
-      </c>
-      <c r="C67" t="s" s="2">
-        <v>429</v>
-      </c>
+        <v>421</v>
+      </c>
+      <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
         <v>79</v>
       </c>
@@ -8974,22 +8911,24 @@
         <v>79</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>430</v>
+        <v>274</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>431</v>
+        <v>422</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>432</v>
-      </c>
-      <c r="N67" t="s" s="2">
-        <v>433</v>
-      </c>
-      <c r="O67" s="2"/>
+        <v>423</v>
+      </c>
+      <c r="N67" s="2"/>
+      <c r="O67" t="s" s="2">
+        <v>424</v>
+      </c>
       <c r="P67" t="s" s="2">
         <v>79</v>
       </c>
-      <c r="Q67" s="2"/>
+      <c r="Q67" t="s" s="2">
+        <v>425</v>
+      </c>
       <c r="R67" t="s" s="2">
         <v>79</v>
       </c>
@@ -9033,19 +8972,19 @@
         <v>79</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>117</v>
+        <v>421</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH67" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="AI67" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ67" t="s" s="2">
-        <v>118</v>
+        <v>101</v>
       </c>
       <c r="AK67" t="s" s="2">
         <v>79</v>
@@ -9054,52 +8993,52 @@
         <v>79</v>
       </c>
     </row>
-    <row r="68" hidden="true">
+    <row r="68">
       <c r="A68" t="s" s="2">
-        <v>434</v>
+        <v>426</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>434</v>
+        <v>426</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
-        <v>356</v>
+        <v>79</v>
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G68" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="H68" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="I68" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="J68" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>110</v>
+        <v>299</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>357</v>
+        <v>427</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>358</v>
-      </c>
-      <c r="N68" t="s" s="2">
-        <v>113</v>
-      </c>
+        <v>428</v>
+      </c>
+      <c r="N68" s="2"/>
       <c r="O68" t="s" s="2">
-        <v>217</v>
+        <v>429</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>79</v>
       </c>
-      <c r="Q68" s="2"/>
+      <c r="Q68" t="s" s="2">
+        <v>430</v>
+      </c>
       <c r="R68" t="s" s="2">
         <v>79</v>
       </c>
@@ -9143,355 +9082,29 @@
         <v>79</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>359</v>
+        <v>426</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH68" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="AI68" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ68" t="s" s="2">
-        <v>118</v>
+        <v>101</v>
       </c>
       <c r="AK68" t="s" s="2">
-        <v>188</v>
+        <v>79</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="s" s="2">
-        <v>435</v>
-      </c>
-      <c r="B69" t="s" s="2">
-        <v>435</v>
-      </c>
-      <c r="C69" s="2"/>
-      <c r="D69" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="E69" s="2"/>
-      <c r="F69" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="G69" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="H69" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="I69" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J69" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="K69" t="s" s="2">
-        <v>436</v>
-      </c>
-      <c r="L69" t="s" s="2">
-        <v>437</v>
-      </c>
-      <c r="M69" t="s" s="2">
-        <v>438</v>
-      </c>
-      <c r="N69" s="2"/>
-      <c r="O69" s="2"/>
-      <c r="P69" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q69" s="2"/>
-      <c r="R69" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S69" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T69" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U69" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V69" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W69" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X69" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y69" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z69" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA69" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB69" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC69" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD69" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE69" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF69" t="s" s="2">
-        <v>435</v>
-      </c>
-      <c r="AG69" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AH69" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AI69" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ69" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK69" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL69" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="s" s="2">
-        <v>439</v>
-      </c>
-      <c r="B70" t="s" s="2">
-        <v>439</v>
-      </c>
-      <c r="C70" s="2"/>
-      <c r="D70" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="E70" s="2"/>
-      <c r="F70" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G70" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="H70" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="I70" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J70" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="K70" t="s" s="2">
-        <v>274</v>
-      </c>
-      <c r="L70" t="s" s="2">
-        <v>440</v>
-      </c>
-      <c r="M70" t="s" s="2">
-        <v>441</v>
-      </c>
-      <c r="N70" s="2"/>
-      <c r="O70" t="s" s="2">
-        <v>442</v>
-      </c>
-      <c r="P70" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q70" t="s" s="2">
-        <v>443</v>
-      </c>
-      <c r="R70" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S70" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T70" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U70" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V70" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W70" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X70" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y70" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z70" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA70" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB70" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC70" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD70" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE70" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF70" t="s" s="2">
-        <v>439</v>
-      </c>
-      <c r="AG70" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH70" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AI70" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ70" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK70" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL70" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="s" s="2">
-        <v>444</v>
-      </c>
-      <c r="B71" t="s" s="2">
-        <v>444</v>
-      </c>
-      <c r="C71" s="2"/>
-      <c r="D71" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="E71" s="2"/>
-      <c r="F71" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G71" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="H71" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="I71" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J71" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="K71" t="s" s="2">
-        <v>299</v>
-      </c>
-      <c r="L71" t="s" s="2">
-        <v>445</v>
-      </c>
-      <c r="M71" t="s" s="2">
-        <v>446</v>
-      </c>
-      <c r="N71" s="2"/>
-      <c r="O71" t="s" s="2">
-        <v>447</v>
-      </c>
-      <c r="P71" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q71" t="s" s="2">
-        <v>448</v>
-      </c>
-      <c r="R71" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S71" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T71" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U71" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V71" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W71" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X71" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y71" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z71" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA71" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB71" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC71" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD71" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE71" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF71" t="s" s="2">
-        <v>444</v>
-      </c>
-      <c r="AG71" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH71" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AI71" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ71" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK71" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL71" t="s" s="2">
         <v>79</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AL71">
+  <autoFilter ref="A1:AL68">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -9501,7 +9114,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI70">
+  <conditionalFormatting sqref="A2:AI67">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/output/StructureDefinition-pdex-provider-group.xlsx
+++ b/output/StructureDefinition-pdex-provider-group.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-17T22:49:33-04:00</t>
+    <t>2026-03-19T09:51:30-04:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/output/StructureDefinition-pdex-provider-group.xlsx
+++ b/output/StructureDefinition-pdex-provider-group.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-19T09:51:30-04:00</t>
+    <t>2026-03-31T21:00:10-04:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/output/StructureDefinition-pdex-provider-group.xlsx
+++ b/output/StructureDefinition-pdex-provider-group.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-31T21:00:10-04:00</t>
+    <t>2026-05-29T12:37:47-04:00</t>
   </si>
   <si>
     <t>Publisher</t>
